--- a/outputs/evaluation/architecture/design/v4/CF_M05/run_1/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v4/CF_M05/run_1/CF_M05_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.8588</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -590,7 +592,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.7895</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1213,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7655</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1234,7 +1235,6 @@
           <t>['AU_02', 'AU_09']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_14</t>
@@ -1245,7 +1245,6 @@
           <t>portal, spring boot</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1264,7 +1263,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -1315,14 +1313,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1349,13 +1344,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1396,14 +1389,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1429,13 +1419,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1476,14 +1464,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1512,13 +1497,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1559,14 +1542,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1595,13 +1575,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1642,14 +1620,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1674,13 +1649,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1701,7 +1674,6 @@
       <c r="D8" t="n">
         <v>0.9520999999999999</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1722,7 +1694,6 @@
           <t>['AU_01', 'AU_02', 'AU_03', 'AU_04', 'AU_05', 'AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_13</t>
@@ -1733,7 +1704,6 @@
           <t>leader, portal, access control, communication log, scheduler, ordering, gsb</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1752,7 +1722,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -1803,14 +1772,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -1837,13 +1803,11 @@
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU35</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1899,7 +1863,6 @@
           <t>P_04</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -1921,14 +1884,11 @@
       <c r="P10" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1974,13 +1934,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>REST</t>
@@ -2005,13 +1963,11 @@
           <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU28</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2052,14 +2008,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>GSB</t>
@@ -2084,13 +2037,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2131,14 +2082,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -2162,13 +2110,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU33</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2214,13 +2160,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2245,13 +2189,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2292,14 +2234,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Ordering</t>
@@ -2326,13 +2265,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_AU11</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2378,13 +2315,11 @@
           <t>['AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -2410,13 +2345,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2472,7 +2405,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -2492,14 +2424,11 @@
       <c r="P17" t="n">
         <v>62</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2545,13 +2474,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -2575,13 +2502,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2622,7 +2547,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2633,7 +2557,6 @@
           <t>P_01</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2652,14 +2575,11 @@
       <c r="P19" t="n">
         <v>56</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2700,7 +2620,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2711,7 +2630,6 @@
           <t>P_02</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2732,7 +2650,6 @@
       <c r="P20" t="n">
         <v>61</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -2743,7 +2660,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2817,7 +2733,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
@@ -2848,7 +2763,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>leader, portal, access control, communication log, scheduler, ordering, gsb</t>
@@ -2889,7 +2803,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>The data format used is JSON.</t>
@@ -2981,7 +2894,6 @@
           <t>Client (Frontend)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The client, also called the frontEnd, is responsible for the presentation and user experience
@@ -3019,7 +2931,6 @@
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
@@ -3057,7 +2968,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -3096,7 +3006,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -3132,7 +3041,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -3169,7 +3077,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
@@ -3207,7 +3114,6 @@
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
@@ -3245,7 +3151,6 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
@@ -3283,7 +3188,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3296,7 +3200,6 @@
           <t>AU_15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0.7572</v>
       </c>
@@ -3317,7 +3220,6 @@
           <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>The controllers, through specific
@@ -3355,7 +3257,6 @@
           <t>Business Logic Layer (Services)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Services provide the interface and implementation of all the application's business logic.</t>
@@ -3391,7 +3292,6 @@
           <t>Domain Layer (Models)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Models represent the internal and persistent structure of the system entities, reflecting the
@@ -3428,7 +3328,6 @@
           <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
@@ -3465,7 +3364,6 @@
           <t>Data access layer (Repositories)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>the Repositories are responsible for performing queries on the database.</t>
@@ -3496,7 +3394,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client (frontend), amazon eks</t>
@@ -3532,7 +3429,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>client (frontend), server (backend)</t>
@@ -3568,7 +3464,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -3584,7 +3479,6 @@
           <t>AU_14</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>0.7174</v>
       </c>
@@ -3600,7 +3494,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -3616,7 +3509,6 @@
           <t>AU_15</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>0.7069</v>
       </c>
@@ -3632,7 +3524,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -3673,7 +3564,6 @@
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
@@ -3710,7 +3600,6 @@
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
@@ -3747,7 +3636,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3760,7 +3648,6 @@
           <t>AU_15</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0.8576</v>
       </c>
